--- a/data/gravel/Ribble AllGrit AL 2025.xlsx
+++ b/data/gravel/Ribble AllGrit AL 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C41D9F-746B-AB4F-89C5-2A103B55EE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139339A8-3C2C-484A-9E8C-0A9BB94FC9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="3880" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1320" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -357,6 +357,24 @@
   </si>
   <si>
     <t>395 estimated</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>gravel</t>
+  </si>
+  <si>
+    <t>handlebar</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>fork</t>
+  </si>
+  <si>
+    <t>rigid</t>
   </si>
 </sst>
 </file>
@@ -709,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1346,170 +1364,170 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
-        <v>31</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
+      </c>
+      <c r="B39" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>67</v>
+        <v>110</v>
+      </c>
+      <c r="B40" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>112</v>
+      </c>
+      <c r="B41" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42">
-        <v>50</v>
+        <v>31</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>36</v>
-      </c>
-      <c r="B44" s="1"/>
+        <v>33</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>67</v>
+        <v>34</v>
+      </c>
+      <c r="B45">
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>38</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>39</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B47" s="1"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>45</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>54</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B63" s="1"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>67</v>
@@ -1517,23 +1535,23 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>67</v>
@@ -1541,7 +1559,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>67</v>
@@ -1549,27 +1567,51 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>59</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71">
-        <v>2405</v>
+        <v>60</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>99</v>
       </c>
     </row>

--- a/data/gravel/Ribble AllGrit AL 2025.xlsx
+++ b/data/gravel/Ribble AllGrit AL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel copy/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139339A8-3C2C-484A-9E8C-0A9BB94FC9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C73784-719E-2E4B-9763-8340F60E6A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -1431,9 +1431,7 @@
       <c r="A48" t="s">
         <v>37</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>67</v>
-      </c>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">

--- a/data/gravel/Ribble AllGrit AL 2025.xlsx
+++ b/data/gravel/Ribble AllGrit AL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C73784-719E-2E4B-9763-8340F60E6A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2B89AF-4D30-FC49-9332-615B7854927F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>rigid</t>
+  </si>
+  <si>
+    <t>https://cdn.speedsize.com/4190f681-07cb-43aa-92d2-6096b01e7b62/https://checkout.ribblecycles.co.uk/media/catalog/product/a/l/allgrit_al_bgravalg2apaxxp_0001_1__2.png/w_1200</t>
   </si>
 </sst>
 </file>
@@ -774,6 +777,11 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:7">
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+    </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Ribble AllGrit AL 2025.xlsx
+++ b/data/gravel/Ribble AllGrit AL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2B89AF-4D30-FC49-9332-615B7854927F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF8D608-CCB7-7E45-9192-F0B8F42D3F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -332,9 +332,6 @@
     <t>48/31</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>https://www.ribblecycles.co.uk/ribble-allgrit-al/</t>
   </si>
   <si>
@@ -378,6 +375,15 @@
   </si>
   <si>
     <t>https://cdn.speedsize.com/4190f681-07cb-43aa-92d2-6096b01e7b62/https://checkout.ribblecycles.co.uk/media/catalog/product/a/l/allgrit_al_bgravalg2apaxxp_0001_1__2.png/w_1200</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Preston, Lancashire, United Kingdom</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -730,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -750,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -774,12 +780,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="B6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -787,7 +793,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="21">
@@ -1140,7 +1146,7 @@
         <v>24</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1300,7 +1306,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C35">
         <v>159</v>
@@ -1320,7 +1326,7 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C36">
         <v>169</v>
@@ -1355,7 +1361,7 @@
         <v>80</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="21">
@@ -1372,26 +1378,26 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" t="s">
         <v>108</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
+        <v>109</v>
+      </c>
+      <c r="B40" t="s">
         <v>110</v>
-      </c>
-      <c r="B40" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
         <v>112</v>
-      </c>
-      <c r="B41" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1399,7 +1405,7 @@
         <v>31</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1618,7 +1624,15 @@
         <v>65</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>99</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>114</v>
+      </c>
+      <c r="B77" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Ribble AllGrit AL 2025.xlsx
+++ b/data/gravel/Ribble AllGrit AL 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF8D608-CCB7-7E45-9192-F0B8F42D3F7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4A4FC4-06F5-744F-859F-E1E32AACA9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1320" yWindow="500" windowWidth="24920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -384,6 +384,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -736,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1469,125 +1487,107 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>47</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>54</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>55</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>58</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>67</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B69" s="1"/>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>59</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>67</v>
@@ -1595,43 +1595,91 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>63</v>
-      </c>
-      <c r="B74">
-        <v>2405</v>
+        <v>57</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
+        <v>60</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
         <v>114</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B83" t="s">
         <v>115</v>
       </c>
     </row>
